--- a/output_plant/stomata_Intermediate_maxbauer_2014.xlsx
+++ b/output_plant/stomata_Intermediate_maxbauer_2014.xlsx
@@ -618,7 +618,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Uintan-Duchesnean NALMA</t>
+    <t xml:space="preserve">Uintan-Duchesnean NALMA; Biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Cupressaceae / Metasequoia</t>
